--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_i_peringrmin_a_2023.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_i_peringrmin_a_2023.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:47</t>
+    <t xml:space="preserve">2026-09-24 01:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -739,10 +739,10 @@
         <v>22</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="17">
@@ -753,10 +753,10 @@
         <v>22</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.07</v>
+        <v>0.05</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="18">
@@ -767,10 +767,10 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="19">
@@ -809,10 +809,10 @@
         <v>28</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.19</v>
+        <v>0.06</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22">
@@ -823,10 +823,10 @@
         <v>28</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.11</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="23">
@@ -837,10 +837,10 @@
         <v>28</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="24">

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_i_peringrmin_a_2023.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_i_peringrmin_a_2023.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:37</t>
+    <t xml:space="preserve">2026-10-01 23:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -515,7 +515,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="31.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="33.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="14.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_i_peringrmin_a_2023.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_i_peringrmin_a_2023.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:04</t>
+    <t xml:space="preserve">2026-10-05 19:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
